--- a/public/examples/gamuda-malaysia-pnl-fy2024-fy2025.xlsx
+++ b/public/examples/gamuda-malaysia-pnl-fy2024-fy2025.xlsx
@@ -122,7 +122,7 @@
     <t>Net profit exceeds operating profit in the thin quarters — Gamuda's JV/associate income (concessions, overseas JVs) sits below the operating line. The analyser trusts the Net Profit column, so this is intentional.</t>
   </si>
   <si>
-    <t>The monthly split inside each quarter is synthesized (30/33/37%) — the group reports quarterly only. Not audited monthly accounts.</t>
+    <t>The monthly split inside each quarter is synthesized (30/33/37%). Not audited monthly accounts.</t>
   </si>
   <si>
     <t>No Units column: construction and property revenue has no single volume metric, so price/volume/mix will not run.</t>
@@ -515,7 +515,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="7" width="20" style="1" customWidth="1"/>
+    <col min="2" max="7" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1104,7 +1104,7 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
